--- a/docs/BEST_Document_Alignment_Tracker.xlsx
+++ b/docs/BEST_Document_Alignment_Tracker.xlsx
@@ -828,7 +828,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>FSD — User creation and login v0.3</t>
+          <t>FSD — User creation and login v0.4</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Screens, rules, messages, tests; role-first; one role per user; S12 Roles list</t>
+          <t>Screens, rules, messages, tests; role-first; one role per user; S12 Roles list; roles built from permission ticks; 14 modules</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>None known. Per-user permissions and module list tagged pending</t>
+          <t>None known. TBR positions tagged pending client confirmation</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Share with client (supersedes v0.2)</t>
+          <t>Share with client (supersedes v0.2 and v0.3)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Folded into FSD v0.3 Figures 1–3</t>
+          <t>Folded into FSD v0.4 Figures 1–3</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>86 permissions in 14 modules, role defaults, 12 open points</t>
+          <t>86 permissions in 14 modules, role defaults, 12 open points (3 decided internally on 28 Oct)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ACC-05 (view switch) removed. Open points await the client; RBAC list not yet received</t>
+          <t>Open points await the client; RBAC list not yet received</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Share with FSD v0.3; merge RBAC list when received</t>
+          <t>Share with FSD v0.4; merge RBAC list when received</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>No Roles list (S12) and no ‘Start from’ on Create role</t>
+          <t>No Roles list (S12); Create role still uses None/View/Edit per module, not permission ticks and scope</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Add when design resumes</t>
+          <t>Update to FSD v0.4 when design resumes</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1192,7 +1192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PRD v3.0 compared with later decisions. After the 28 October consolidation every row is reflected in PRD v3.1, FSD v0.3 and the permission catalogue; rows awaiting the client are tagged PENDING CLIENT CONFIRMATION there.</t>
+          <t>PRD v3.0 compared with later decisions. After the 28 October consolidation every row is reflected in PRD v3.1, FSD v0.4 and the permission catalogue; rows awaiting the client are tagged PENDING CLIENT CONFIRMATION there.</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>PRD v3.1 §7.4, §8.11; FSD v0.3</t>
+          <t>PRD v3.1 §7.4, §8.11; FSD v0.4</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>PRD v3.1 §7.1, §8.1; FSD v0.3</t>
+          <t>PRD v3.1 §7.1, §8.1; FSD v0.4</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>PRD v3.1 §4, §7.1, §7.4, §8.9, §16; FSD v0.3; catalogue (ACC-05 removed)</t>
+          <t>PRD v3.1 §4, §7.1, §7.4, §8.9, §16; FSD v0.4; catalogue (ACC-05 removed)</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>None outside the role; edit the role or create a new one</t>
+          <t>None outside the role; edit the role or create a new one (confirmed internally 28 Oct, D-021)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Role-first proposal 27 Oct</t>
+          <t>Role-first proposal 27 Oct; D-021</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>FSD v0.3 BR-07; PRD v3.1 §7.4, §11 (tagged)</t>
+          <t>FSD v0.4 BR-07; PRD v3.1 §7.4, §11 (tagged)</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>PRD v3.1 §8.1; FSD v0.3 BR-18</t>
+          <t>PRD v3.1 §8.1; FSD v0.4 BR-18</t>
         </is>
       </c>
     </row>
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Catalogue proposes 14 (adds My account, Supervision, Devices, Support access)</t>
+          <t>14 modules (adds My account, Supervision, Devices, Support access)</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Catalogue 27 Oct</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Awaiting client</t>
+          <t>D-021, 28 Oct</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Agreed internally</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>FSD v0.3 §2.2 (tagged); catalogue open point 4</t>
+          <t>FSD v0.4 §2.2 (tagged); catalogue open point 4</t>
         </is>
       </c>
     </row>
@@ -2089,28 +2089,63 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Catalogue suggests ticks per permission, grouped by module</t>
+          <t>Ticks per permission, grouped by module, with a scope per permission</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Catalogue 27 Oct</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Awaiting client</t>
+          <t>D-021, 28 Oct</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Agreed internally</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>FSD v0.3 §2.2 (tagged); catalogue open point 11</t>
+          <t>FSD v0.4 §2.2, S4, BR-26 (tagged); catalogue open point 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Org Admin and sessions</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>FSD v0.4: Org Admin has no Sessions access; D-014: Org Admin schedules sessions</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Scheduling only (SES-01 to SES-05); no session content</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>D-021, 28 Oct</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Agreed internally</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>FSD v0.4 §2.2 (tagged); catalogue open point 12</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Agreed,Agreed in review,Agreed internally,Awaiting client,Pending client,Needs decision"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/BEST_Document_Alignment_Tracker.xlsx
+++ b/docs/BEST_Document_Alignment_Tracker.xlsx
@@ -55,7 +55,7 @@
       <sz val="10.5"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +92,11 @@
         <fgColor rgb="00E3F5EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -110,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +141,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1170,7 +1178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2143,9 +2151,44 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Platform master data (D-022)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Not in PRD v3.1, catalogue or schema</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Consent items, assessment types and validity, client profiles, checklist library, devices, signal parameters, reason lists, client fields</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>D-022, 28 Oct</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Needs decision</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Kept open by Sujit: PRD §8.12, §8.13; catalogue (3 new permissions); schema (new collections)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F5:F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Agreed,Agreed in review,Agreed internally,Awaiting client,Pending client,Needs decision"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/BEST_Document_Alignment_Tracker.xlsx
+++ b/docs/BEST_Document_Alignment_Tracker.xlsx
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>MongoDB schema (user creation)</t>
+          <t>MongoDB schema</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>13 collections for user creation and login</t>
+          <t>26 collections: user creation and login (13) and platform master data (13, D-022)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Follows role-first and D-019</t>
+          <t>Follows D-019, D-021, D-022</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Kept open by Sujit: PRD §8.12, §8.13; catalogue (3 new permissions); schema (new collections)</t>
+          <t>In the schema (28 Oct). Still open: PRD §8.12, §8.13; catalogue and FSD §2.2 (3 new Clinic settings permissions: checklists, reason lists, client fields)</t>
         </is>
       </c>
     </row>
